--- a/Linear Systems/DATAMSD.xlsx
+++ b/Linear Systems/DATAMSD.xlsx
@@ -44,7 +44,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2">
         <v>10</v>
       </c>
@@ -430,7 +430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
         <v>9.20254519829449</v>
       </c>
@@ -438,7 +438,7 @@
         <v>-1.357793949246876</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
         <v>9.692141086320511</v>
       </c>
@@ -446,7 +446,7 @@
         <v>-0.09435309320796414</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3">
         <v>10.17374575609728</v>
       </c>
@@ -454,7 +454,7 @@
         <v>-2.529250997572725</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3">
         <v>9.233209543929458</v>
       </c>
@@ -462,7 +462,7 @@
         <v>-3.624094830493781</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3">
         <v>9.36287808977275</v>
       </c>
@@ -470,7 +470,7 @@
         <v>-3.5813589583134</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3">
         <v>9.79099195581673</v>
       </c>
@@ -478,7 +478,7 @@
         <v>-5.776112573110677</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3">
         <v>9.41054775345911</v>
       </c>
@@ -486,7 +486,7 @@
         <v>-5.837284581031726</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3">
         <v>9.69032265916067</v>
       </c>
@@ -494,7 +494,7 @@
         <v>-6.663172393821802</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3">
         <v>9.574005947718117</v>
       </c>
@@ -502,7 +502,7 @@
         <v>-6.58114945562162</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3">
         <v>11.51609631862426</v>
       </c>
@@ -510,7 +510,7 @@
         <v>-8.668031763089912</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3">
         <v>10.0582176783471</v>
       </c>
@@ -518,7 +518,7 @@
         <v>-8.16903451163729</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3">
         <v>11.63460327903671</v>
       </c>
@@ -526,7 +526,7 @@
         <v>-11.03989504476965</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3">
         <v>9.064354360741216</v>
       </c>
@@ -534,7 +534,7 @@
         <v>-10.58760494114708</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3">
         <v>10.82386780384578</v>
       </c>
@@ -542,7 +542,7 @@
         <v>-11.0014294987139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3">
         <v>9.81635179426276</v>
       </c>
@@ -550,7 +550,7 @@
         <v>-12.18180428728948</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3">
         <v>9.532460006545458</v>
       </c>
@@ -558,7 +558,7 @@
         <v>-13.37841463105757</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3">
         <v>9.242369202271407</v>
       </c>
@@ -566,7 +566,7 @@
         <v>-13.99031011676913</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3">
         <v>9.647904189997897</v>
       </c>
@@ -574,7 +574,7 @@
         <v>-13.28190737038121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3">
         <v>9.685986676590888</v>
       </c>
@@ -582,7 +582,7 @@
         <v>-16.12925082538318</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3">
         <v>8.433114356398406</v>
       </c>
@@ -590,7 +590,7 @@
         <v>-17.71078231721226</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3">
         <v>10.11632448324989</v>
       </c>
@@ -598,7 +598,7 @@
         <v>-18.41264070204597</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3">
         <v>9.604596597048648</v>
       </c>
@@ -606,7 +606,7 @@
         <v>-18.49255321992321</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3">
         <v>9.538709735023435</v>
       </c>
@@ -614,7 +614,7 @@
         <v>-19.51580872678051</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3">
         <v>8.438496956356158</v>
       </c>
